--- a/Benchmarks/Water Chemistry/Conductivity/Cond_Spearmans_Matrix.xlsx
+++ b/Benchmarks/Water Chemistry/Conductivity/Cond_Spearmans_Matrix.xlsx
@@ -7409,4 +7409,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{db79d039-fcd0-4045-9c78-4cfb2eba0904}" enabled="1" method="Privileged" siteId="{aa3f6932-fa7c-47b4-a0ce-a598cad161cf}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/Benchmarks/Water Chemistry/Conductivity/Cond_Spearmans_Matrix.xlsx
+++ b/Benchmarks/Water Chemistry/Conductivity/Cond_Spearmans_Matrix.xlsx
@@ -7413,6 +7413,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{db79d039-fcd0-4045-9c78-4cfb2eba0904}" enabled="1" method="Privileged" siteId="{aa3f6932-fa7c-47b4-a0ce-a598cad161cf}" contentBits="0" removed="0"/>
+  <clbl:label id="{db79d039-fcd0-4045-9c78-4cfb2eba0904}" enabled="1" method="Privileged" siteId="{aa3f6932-fa7c-47b4-a0ce-a598cad161cf}" removed="0"/>
 </clbl:labelList>
 </file>